--- a/tasks/finalpool/yf-sector-comparison-gform-excel-email/groundtruth_workspace/Sector_Comparison.xlsx
+++ b/tasks/finalpool/yf-sector-comparison-gform-excel-email/groundtruth_workspace/Sector_Comparison.xlsx
@@ -488,7 +488,7 @@
         <v>349</v>
       </c>
       <c r="H2" t="n">
-        <v>129.8688</v>
+        <v>140.53</v>
       </c>
     </row>
     <row r="3">
@@ -499,7 +499,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amazon.com Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -520,7 +520,7 @@
         <v>258.6</v>
       </c>
       <c r="H3" t="n">
-        <v>151.61</v>
+        <v>161.38</v>
       </c>
     </row>
     <row r="4">
@@ -549,10 +549,10 @@
         <v>14.66</v>
       </c>
       <c r="G4" t="n">
-        <v>335.87</v>
+        <v>337.25</v>
       </c>
       <c r="H4" t="n">
-        <v>172.6763</v>
+        <v>202.16</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         <v>251.71</v>
       </c>
       <c r="H5" t="n">
-        <v>134.9218</v>
+        <v>141.5</v>
       </c>
     </row>
     <row r="6">
@@ -616,7 +616,7 @@
         <v>159.61</v>
       </c>
       <c r="H6" t="n">
-        <v>94.5513</v>
+        <v>97.8</v>
       </c>
     </row>
   </sheetData>
